--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -529,12 +529,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Error:</t>
+          <t>Error: Creation failure: 409, detail= Creation validation failed. Multiple matching users were found: &lt;users&gt;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,138 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Error: creation failure: code= 400, detail= Creation validation failed. User created, these attributes were not updated: &lt;list&gt;.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M4X204WZGGM62ZSW6DGNMAWY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X204WZGGM62ZSW6DGNMAWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Error: update failure: code 400, detail= Update validation failed. These attributes were not updated: &lt;lists&gt;.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M4X57XPGYQD8J179YMXHJAYF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X57XPGYQD8J179YMXHJAYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M4X5AMCJQKXTG5Q91YDVVGEG</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5AMCJQKXTG5Q91YDVVGEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Error: update failure: code= 404, detail= Update validation failed. The user was not found.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M4X5B81RZZMESA4W2G1F84RZ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5B81RZZMESA4W2G1F84RZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01M4X5DCY0A19M28HKPHHNFGV2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5DCY0A19M28HKPHHNFGV2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +702,50 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Error: deactivation failure, code 400, detail= Deactivation validation failed. &lt;user&gt; is still active.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M4YV18B23T2FT2AVJ3A97J87</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YV18B23T2FT2AVJ3A97J87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,116 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Error: Access denied: Okta XaaS isn't enabled for your account. Please contact Okta Support.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Error: The Okta import process returned an error. Please review the Okta UI and the identity source session details.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Error: &lt;operation&gt;: import session timed out after &lt;n&gt; polling attempts &lt;operation&gt;</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -649,12 +649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M4X5AMCJQKXTG5Q91YDVVGEG</t>
+          <t>h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5AMCJQKXTG5Q91YDVVGEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
         </is>
       </c>
     </row>

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,6 +856,28 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M51CZH5M2DD9HDCX41QVYQJ5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M51CZH5M2DD9HDCX41QVYQJ5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Error: update failure: code 400, detail= Update validation failed. These attributes were not updated: &lt;lists&gt;.</t>
+          <t>Error: update failure: code 400, detail= Update validation failed. These attributes were not updated: &lt;list&gt;.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">

--- a/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Troubleshooting-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Troubleshooting</t>
+          <t>Common Errors</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,394 +485,416 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Error: Creation validation failed. No matching user was found using the configured correlation attribute.</t>
+          <t>Troubleshooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01M4THMKBZ7PDJTPABDD88NEAZ</t>
+          <t>h_01M5F79XR0SGSWGCKHYYFMCFPK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THMKBZ7PDJTPABDD88NEAZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M5F79XR0SGSWGCKHYYFMCFPK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: Creation validation failed. No matching user was found using the configured correlation attribute.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01M4THMQ4VX154Q4Y5Y0MBDKR0</t>
+          <t>h_01M4THMKBZ7PDJTPABDD88NEAZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THMQ4VX154Q4Y5Y0MBDKR0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THMKBZ7PDJTPABDD88NEAZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Error: Creation failure: 409, detail= Creation validation failed. Multiple matching users were found: &lt;users&gt;</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01M4THNKZ5D59FARESCQ823GJ0</t>
+          <t>h_01M4THMQ4VX154Q4Y5Y0MBDKR0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THNKZ5D59FARESCQ823GJ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THMQ4VX154Q4Y5Y0MBDKR0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: creation failure: 409, detail= Creation validation failed. Multiple matching users were found: &lt;users&gt;</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01M4THNR78GXYYMHNZA3NDA2ZF</t>
+          <t>h_01M4THNKZ5D59FARESCQ823GJ0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THNR78GXYYMHNZA3NDA2ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THNKZ5D59FARESCQ823GJ0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Error: creation failure: code= 400, detail= Creation validation failed. User created, these attributes were not updated: &lt;list&gt;.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
+          <t>h_01M4THNR78GXYYMHNZA3NDA2ZF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4THNR78GXYYMHNZA3NDA2ZF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: creation failure: code= 400, detail= Creation validation failed. User created, these attributes were not updated: &lt;list&gt;.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01M4X204WZGGM62ZSW6DGNMAWY</t>
+          <t>h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X204WZGGM62ZSW6DGNMAWY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X1WKFA6ZV47NNPXH9WYG4S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Error: update failure: code 400, detail= Update validation failed. These attributes were not updated: &lt;list&gt;.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M4X57XPGYQD8J179YMXHJAYF</t>
+          <t>h_01M4X204WZGGM62ZSW6DGNMAWY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X57XPGYQD8J179YMXHJAYF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X204WZGGM62ZSW6DGNMAWY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: update failure: code 400, detail= Update validation failed. These attributes were not updated: &lt;list&gt;.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
+          <t>h_01M4X57XPGYQD8J179YMXHJAYF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X57XPGYQD8J179YMXHJAYF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Error: update failure: code= 404, detail= Update validation failed. The user was not found.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01M4X5B81RZZMESA4W2G1F84RZ</t>
+          <t>h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5B81RZZMESA4W2G1F84RZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZS1NJDGDGK8D4WSYHT5S8G</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: update failure: code= 404, detail= Update validation failed. The user was not found.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01M4X5DCY0A19M28HKPHHNFGV2</t>
+          <t>h_01M4X5B81RZZMESA4W2G1F84RZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5DCY0A19M28HKPHHNFGV2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5B81RZZMESA4W2G1F84RZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Error: deactivation failure, code 400, detail= Deactivation validation failed. &lt;user&gt; is still active.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
+          <t>h_01M4X5DCY0A19M28HKPHHNFGV2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4X5DCY0A19M28HKPHHNFGV2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: deactivation failure, code 400, detail= Deactivation validation failed. &lt;user&gt; is still active.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01M4YV18B23T2FT2AVJ3A97J87</t>
+          <t>h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YV18B23T2FT2AVJ3A97J87</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YTTX25F3CBYAEG8A7Q05RQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Error: Access denied: Okta XaaS isn't enabled for your account. Please contact Okta Support.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
+          <t>h_01M4YV18B23T2FT2AVJ3A97J87</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4YV18B23T2FT2AVJ3A97J87</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: Access denied: Okta XaaS isn't enabled for your account. Please contact Okta Support.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
+          <t>h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEA5HWCJG5EMD8QQP15K6J</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Error: The Okta import process returned an error. Please review the Okta UI and the identity source session details.</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
+          <t>h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEBSYZWAFRMJKM6TY1SFVB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solution</t>
+          <t>Error: The Okta import process returned an error. Please review the Okta UI and the identity source session details.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
+          <t>h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEWJN7107VC4WJWRBW1KV5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Error: &lt;operation&gt;: import session timed out after &lt;n&gt; polling attempts &lt;operation&gt;</t>
+          <t>Solution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+          <t>h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZEYCBHDEYFM3ZVC607ZSGA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Error: &lt;operation&gt;: import session timed out after &lt;n&gt; polling attempts</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M4ZGJ3BP9JGCBJHC6T857DQ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01M51CZH5M2DD9HDCX41QVYQJ5</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Troubleshooting-Guide/#h_01M51CZH5M2DD9HDCX41QVYQJ5</t>
         </is>
